--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119689144</v>
+        <v>119689156</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567678</v>
+        <v>567713</v>
       </c>
       <c r="R7" t="n">
-        <v>6410426</v>
+        <v>6410434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119689156</v>
+        <v>119689144</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,35 +1356,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567713</v>
+        <v>567678</v>
       </c>
       <c r="R8" t="n">
-        <v>6410434</v>
+        <v>6410426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119779255</v>
+        <v>119778919</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>90966</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3807,35 +3807,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3843,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567594</v>
+        <v>567595</v>
       </c>
       <c r="R30" t="n">
-        <v>6410487</v>
+        <v>6410463</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3906,10 +3909,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119778919</v>
+        <v>119779255</v>
       </c>
       <c r="B31" t="n">
-        <v>90966</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3918,38 +3921,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567595</v>
+        <v>567594</v>
       </c>
       <c r="R31" t="n">
-        <v>6410463</v>
+        <v>6410487</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119689156</v>
+        <v>119689144</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1245,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567713</v>
+        <v>567678</v>
       </c>
       <c r="R7" t="n">
-        <v>6410434</v>
+        <v>6410426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119689144</v>
+        <v>119689156</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567678</v>
+        <v>567713</v>
       </c>
       <c r="R8" t="n">
-        <v>6410426</v>
+        <v>6410434</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119689178</v>
+        <v>119689194</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567713</v>
+        <v>567709</v>
       </c>
       <c r="R2" t="n">
-        <v>6410415</v>
+        <v>6410401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119689293</v>
+        <v>119689104</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567662</v>
+        <v>567688</v>
       </c>
       <c r="R3" t="n">
-        <v>6410431</v>
+        <v>6410378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119689104</v>
+        <v>119689280</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567688</v>
+        <v>567664</v>
       </c>
       <c r="R4" t="n">
-        <v>6410378</v>
+        <v>6410428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119689109</v>
+        <v>119689165</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567689</v>
+        <v>567711</v>
       </c>
       <c r="R5" t="n">
-        <v>6410384</v>
+        <v>6410421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119689355</v>
+        <v>119689144</v>
       </c>
       <c r="B6" t="n">
-        <v>91185</v>
+        <v>90582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567675</v>
+        <v>567678</v>
       </c>
       <c r="R6" t="n">
-        <v>6410414</v>
+        <v>6410426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119689144</v>
+        <v>119689258</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567678</v>
+        <v>567693</v>
       </c>
       <c r="R7" t="n">
-        <v>6410426</v>
+        <v>6410380</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119689156</v>
+        <v>119689178</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1398,7 +1395,7 @@
         <v>567713</v>
       </c>
       <c r="R8" t="n">
-        <v>6410434</v>
+        <v>6410415</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119689165</v>
+        <v>119689134</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1506,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567711</v>
+        <v>567687</v>
       </c>
       <c r="R9" t="n">
-        <v>6410421</v>
+        <v>6410413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119689329</v>
+        <v>119689293</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1617,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567672</v>
+        <v>567662</v>
       </c>
       <c r="R10" t="n">
-        <v>6410430</v>
+        <v>6410431</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119689280</v>
+        <v>119689109</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1728,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567664</v>
+        <v>567689</v>
       </c>
       <c r="R11" t="n">
-        <v>6410428</v>
+        <v>6410384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119689194</v>
+        <v>119689355</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,35 +1800,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567709</v>
+        <v>567675</v>
       </c>
       <c r="R12" t="n">
-        <v>6410401</v>
+        <v>6410414</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119689258</v>
+        <v>119689156</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567693</v>
+        <v>567713</v>
       </c>
       <c r="R13" t="n">
-        <v>6410380</v>
+        <v>6410434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119689134</v>
+        <v>119689329</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567687</v>
+        <v>567672</v>
       </c>
       <c r="R14" t="n">
-        <v>6410413</v>
+        <v>6410430</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119779279</v>
+        <v>119779026</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567585</v>
+        <v>567602</v>
       </c>
       <c r="R15" t="n">
-        <v>6410476</v>
+        <v>6410466</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119779026</v>
+        <v>119779098</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567602</v>
+        <v>567625</v>
       </c>
       <c r="R16" t="n">
-        <v>6410466</v>
+        <v>6410464</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119778981</v>
+        <v>119779265</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567600</v>
+        <v>567592</v>
       </c>
       <c r="R17" t="n">
-        <v>6410463</v>
+        <v>6410490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119779062</v>
+        <v>119779211</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567621</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6410474</v>
+        <v>6410473</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119778822</v>
+        <v>119779279</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567611</v>
+        <v>567585</v>
       </c>
       <c r="R19" t="n">
-        <v>6410497</v>
+        <v>6410476</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119779192</v>
+        <v>119779223</v>
       </c>
       <c r="B20" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,38 +2691,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2730,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567594</v>
+        <v>567616</v>
       </c>
       <c r="R20" t="n">
-        <v>6410459</v>
+        <v>6410471</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119779131</v>
+        <v>119779242</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2841,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567618</v>
+        <v>567625</v>
       </c>
       <c r="R21" t="n">
-        <v>6410460</v>
+        <v>6410461</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,7 +2901,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119779153</v>
+        <v>119778822</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2952,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567606</v>
+        <v>567611</v>
       </c>
       <c r="R22" t="n">
-        <v>6410463</v>
+        <v>6410497</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,10 +3012,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119778955</v>
+        <v>119778981</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3027,38 +3024,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3066,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567588</v>
+        <v>567600</v>
       </c>
       <c r="R23" t="n">
-        <v>6410471</v>
+        <v>6410463</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119779242</v>
+        <v>119779192</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3141,35 +3135,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3177,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567625</v>
+        <v>567594</v>
       </c>
       <c r="R24" t="n">
-        <v>6410461</v>
+        <v>6410459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3240,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119779247</v>
+        <v>119779131</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3288,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567624</v>
+        <v>567618</v>
       </c>
       <c r="R25" t="n">
-        <v>6410463</v>
+        <v>6410460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,7 +3348,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119779265</v>
+        <v>119779255</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3399,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567592</v>
+        <v>567594</v>
       </c>
       <c r="R26" t="n">
-        <v>6410490</v>
+        <v>6410487</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,10 +3459,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119778854</v>
+        <v>119778955</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3474,35 +3471,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567604</v>
+        <v>567588</v>
       </c>
       <c r="R27" t="n">
-        <v>6410461</v>
+        <v>6410471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119779223</v>
+        <v>119778919</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>90966</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3585,35 +3585,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3621,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567616</v>
+        <v>567595</v>
       </c>
       <c r="R28" t="n">
-        <v>6410471</v>
+        <v>6410463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,7 +3687,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119779211</v>
+        <v>119779247</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3732,10 +3735,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567628</v>
+        <v>567624</v>
       </c>
       <c r="R29" t="n">
-        <v>6410473</v>
+        <v>6410463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,10 +3798,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119778919</v>
+        <v>119778854</v>
       </c>
       <c r="B30" t="n">
-        <v>90966</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3807,38 +3810,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567595</v>
+        <v>567604</v>
       </c>
       <c r="R30" t="n">
-        <v>6410463</v>
+        <v>6410461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119779255</v>
+        <v>119779153</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567594</v>
+        <v>567606</v>
       </c>
       <c r="R31" t="n">
-        <v>6410487</v>
+        <v>6410463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119779098</v>
+        <v>119779062</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567625</v>
+        <v>567621</v>
       </c>
       <c r="R32" t="n">
-        <v>6410464</v>
+        <v>6410474</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119689165</v>
+        <v>119689144</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567711</v>
+        <v>567678</v>
       </c>
       <c r="R5" t="n">
-        <v>6410421</v>
+        <v>6410426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119689144</v>
+        <v>119689165</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,38 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567678</v>
+        <v>567711</v>
       </c>
       <c r="R6" t="n">
-        <v>6410426</v>
+        <v>6410421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119689194</v>
+        <v>119689178</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567709</v>
+        <v>567713</v>
       </c>
       <c r="R2" t="n">
-        <v>6410401</v>
+        <v>6410415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119689104</v>
+        <v>119689109</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567688</v>
+        <v>567689</v>
       </c>
       <c r="R3" t="n">
-        <v>6410378</v>
+        <v>6410384</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119689280</v>
+        <v>119689329</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567664</v>
+        <v>567672</v>
       </c>
       <c r="R4" t="n">
-        <v>6410428</v>
+        <v>6410430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119689165</v>
+        <v>119689156</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567711</v>
+        <v>567713</v>
       </c>
       <c r="R6" t="n">
-        <v>6410421</v>
+        <v>6410434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119689258</v>
+        <v>119689280</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567693</v>
+        <v>567664</v>
       </c>
       <c r="R7" t="n">
-        <v>6410380</v>
+        <v>6410428</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119689178</v>
+        <v>119689194</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567713</v>
+        <v>567709</v>
       </c>
       <c r="R8" t="n">
-        <v>6410415</v>
+        <v>6410401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119689134</v>
+        <v>119689258</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567687</v>
+        <v>567693</v>
       </c>
       <c r="R9" t="n">
-        <v>6410413</v>
+        <v>6410380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119689109</v>
+        <v>119689165</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567689</v>
+        <v>567711</v>
       </c>
       <c r="R11" t="n">
-        <v>6410384</v>
+        <v>6410421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119689156</v>
+        <v>119689134</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567713</v>
+        <v>567687</v>
       </c>
       <c r="R13" t="n">
-        <v>6410434</v>
+        <v>6410413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119689329</v>
+        <v>119689104</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567672</v>
+        <v>567688</v>
       </c>
       <c r="R14" t="n">
-        <v>6410430</v>
+        <v>6410378</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119779098</v>
+        <v>119778981</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567625</v>
+        <v>567600</v>
       </c>
       <c r="R16" t="n">
-        <v>6410464</v>
+        <v>6410463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119779265</v>
+        <v>119778854</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567592</v>
+        <v>567604</v>
       </c>
       <c r="R17" t="n">
-        <v>6410490</v>
+        <v>6410461</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119779211</v>
+        <v>119779255</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567594</v>
       </c>
       <c r="R18" t="n">
-        <v>6410473</v>
+        <v>6410487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119779279</v>
+        <v>119779153</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567585</v>
+        <v>567606</v>
       </c>
       <c r="R19" t="n">
-        <v>6410476</v>
+        <v>6410463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119779223</v>
+        <v>119779131</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567616</v>
+        <v>567618</v>
       </c>
       <c r="R20" t="n">
-        <v>6410471</v>
+        <v>6410460</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119779242</v>
+        <v>119778955</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,35 +2802,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2838,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567625</v>
+        <v>567588</v>
       </c>
       <c r="R21" t="n">
-        <v>6410461</v>
+        <v>6410471</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,7 +2904,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119778822</v>
+        <v>119779098</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2949,10 +2952,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567611</v>
+        <v>567625</v>
       </c>
       <c r="R22" t="n">
-        <v>6410497</v>
+        <v>6410464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,7 +3015,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119778981</v>
+        <v>119779265</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -3060,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567600</v>
+        <v>567592</v>
       </c>
       <c r="R23" t="n">
-        <v>6410463</v>
+        <v>6410490</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119779192</v>
+        <v>119779062</v>
       </c>
       <c r="B24" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,38 +3138,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567594</v>
+        <v>567621</v>
       </c>
       <c r="R24" t="n">
-        <v>6410459</v>
+        <v>6410474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,10 +3237,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119779131</v>
+        <v>119778919</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>90966</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3249,35 +3249,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3285,10 +3288,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567618</v>
+        <v>567595</v>
       </c>
       <c r="R25" t="n">
-        <v>6410460</v>
+        <v>6410463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119779255</v>
+        <v>119779192</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,35 +3363,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3399,7 +3405,7 @@
         <v>567594</v>
       </c>
       <c r="R26" t="n">
-        <v>6410487</v>
+        <v>6410459</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3459,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119778955</v>
+        <v>119779223</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,38 +3477,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3510,7 +3513,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567588</v>
+        <v>567616</v>
       </c>
       <c r="R27" t="n">
         <v>6410471</v>
@@ -3573,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119778919</v>
+        <v>119778822</v>
       </c>
       <c r="B28" t="n">
-        <v>90966</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3585,38 +3588,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567595</v>
+        <v>567611</v>
       </c>
       <c r="R28" t="n">
-        <v>6410463</v>
+        <v>6410497</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119779247</v>
+        <v>119779279</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567624</v>
+        <v>567585</v>
       </c>
       <c r="R29" t="n">
-        <v>6410463</v>
+        <v>6410476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119778854</v>
+        <v>119779247</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567604</v>
+        <v>567624</v>
       </c>
       <c r="R30" t="n">
-        <v>6410461</v>
+        <v>6410463</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119779153</v>
+        <v>119779242</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567606</v>
+        <v>567625</v>
       </c>
       <c r="R31" t="n">
-        <v>6410463</v>
+        <v>6410461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119779062</v>
+        <v>119779211</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567621</v>
+        <v>567628</v>
       </c>
       <c r="R32" t="n">
-        <v>6410474</v>
+        <v>6410473</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119689178</v>
+        <v>119689165</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567713</v>
+        <v>567711</v>
       </c>
       <c r="R2" t="n">
-        <v>6410415</v>
+        <v>6410421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119689109</v>
+        <v>119689258</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567689</v>
+        <v>567693</v>
       </c>
       <c r="R3" t="n">
-        <v>6410384</v>
+        <v>6410380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119689329</v>
+        <v>119689355</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567672</v>
+        <v>567675</v>
       </c>
       <c r="R4" t="n">
-        <v>6410430</v>
+        <v>6410414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119689144</v>
+        <v>119689194</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567678</v>
+        <v>567709</v>
       </c>
       <c r="R5" t="n">
-        <v>6410426</v>
+        <v>6410401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119689280</v>
+        <v>119689293</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567664</v>
+        <v>567662</v>
       </c>
       <c r="R7" t="n">
-        <v>6410428</v>
+        <v>6410431</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119689194</v>
+        <v>119689109</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567709</v>
+        <v>567689</v>
       </c>
       <c r="R8" t="n">
-        <v>6410401</v>
+        <v>6410384</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119689258</v>
+        <v>119689144</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,35 +1467,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567693</v>
+        <v>567678</v>
       </c>
       <c r="R9" t="n">
-        <v>6410380</v>
+        <v>6410426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119689293</v>
+        <v>119689280</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1614,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567662</v>
+        <v>567664</v>
       </c>
       <c r="R10" t="n">
-        <v>6410431</v>
+        <v>6410428</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119689165</v>
+        <v>119689104</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1725,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567711</v>
+        <v>567688</v>
       </c>
       <c r="R11" t="n">
-        <v>6410421</v>
+        <v>6410378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119689355</v>
+        <v>119689134</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,38 +1803,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567675</v>
+        <v>567687</v>
       </c>
       <c r="R12" t="n">
-        <v>6410414</v>
+        <v>6410413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119689134</v>
+        <v>119689329</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567687</v>
+        <v>567672</v>
       </c>
       <c r="R13" t="n">
-        <v>6410413</v>
+        <v>6410430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119689104</v>
+        <v>119689178</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567688</v>
+        <v>567713</v>
       </c>
       <c r="R14" t="n">
-        <v>6410378</v>
+        <v>6410415</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119779026</v>
+        <v>119778919</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90966</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,35 +2136,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2172,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567602</v>
+        <v>567595</v>
       </c>
       <c r="R15" t="n">
-        <v>6410466</v>
+        <v>6410463</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119778981</v>
+        <v>119779026</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2283,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567600</v>
+        <v>567602</v>
       </c>
       <c r="R16" t="n">
-        <v>6410463</v>
+        <v>6410466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2460,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119779255</v>
+        <v>119779098</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2505,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567594</v>
+        <v>567625</v>
       </c>
       <c r="R18" t="n">
-        <v>6410487</v>
+        <v>6410464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2571,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119779153</v>
+        <v>119779223</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2616,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567606</v>
+        <v>567616</v>
       </c>
       <c r="R19" t="n">
-        <v>6410463</v>
+        <v>6410471</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119778955</v>
+        <v>119779265</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,38 +2805,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567588</v>
+        <v>567592</v>
       </c>
       <c r="R21" t="n">
-        <v>6410471</v>
+        <v>6410490</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119779098</v>
+        <v>119779279</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567625</v>
+        <v>567585</v>
       </c>
       <c r="R22" t="n">
-        <v>6410464</v>
+        <v>6410476</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119779265</v>
+        <v>119778955</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3027,35 +3027,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3063,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567592</v>
+        <v>567588</v>
       </c>
       <c r="R23" t="n">
-        <v>6410490</v>
+        <v>6410471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3126,7 +3129,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119779062</v>
+        <v>119778822</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3174,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567621</v>
+        <v>567611</v>
       </c>
       <c r="R24" t="n">
-        <v>6410474</v>
+        <v>6410497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119778919</v>
+        <v>119779192</v>
       </c>
       <c r="B25" t="n">
-        <v>90966</v>
+        <v>90582</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3249,25 +3252,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3288,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567595</v>
+        <v>567594</v>
       </c>
       <c r="R25" t="n">
-        <v>6410463</v>
+        <v>6410459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,10 +3354,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119779192</v>
+        <v>119779242</v>
       </c>
       <c r="B26" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,38 +3366,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567594</v>
+        <v>567625</v>
       </c>
       <c r="R26" t="n">
-        <v>6410459</v>
+        <v>6410461</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119779223</v>
+        <v>119779255</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567616</v>
+        <v>567594</v>
       </c>
       <c r="R27" t="n">
-        <v>6410471</v>
+        <v>6410487</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119778822</v>
+        <v>119779062</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567611</v>
+        <v>567621</v>
       </c>
       <c r="R28" t="n">
-        <v>6410497</v>
+        <v>6410474</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119779279</v>
+        <v>119778981</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567585</v>
+        <v>567600</v>
       </c>
       <c r="R29" t="n">
-        <v>6410476</v>
+        <v>6410463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119779247</v>
+        <v>119779153</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567624</v>
+        <v>567606</v>
       </c>
       <c r="R30" t="n">
         <v>6410463</v>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119779242</v>
+        <v>119779247</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567625</v>
+        <v>567624</v>
       </c>
       <c r="R31" t="n">
-        <v>6410461</v>
+        <v>6410463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -2904,10 +2904,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119779279</v>
+        <v>119778955</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2916,35 +2916,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2952,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567585</v>
+        <v>567588</v>
       </c>
       <c r="R22" t="n">
-        <v>6410476</v>
+        <v>6410471</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119778955</v>
+        <v>119779279</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3027,38 +3030,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567588</v>
+        <v>567585</v>
       </c>
       <c r="R23" t="n">
-        <v>6410471</v>
+        <v>6410476</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -2904,10 +2904,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119778955</v>
+        <v>119779279</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2916,38 +2916,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2955,10 +2952,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567588</v>
+        <v>567585</v>
       </c>
       <c r="R22" t="n">
-        <v>6410471</v>
+        <v>6410476</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119779279</v>
+        <v>119778955</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3030,35 +3027,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567585</v>
+        <v>567588</v>
       </c>
       <c r="R23" t="n">
-        <v>6410476</v>
+        <v>6410471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -2127,7 +2127,7 @@
         <v>119778919</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>90984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119779026</v>
+        <v>119779247</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567602</v>
+        <v>567624</v>
       </c>
       <c r="R16" t="n">
-        <v>6410466</v>
+        <v>6410463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119778854</v>
+        <v>119779255</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567604</v>
+        <v>567594</v>
       </c>
       <c r="R17" t="n">
-        <v>6410461</v>
+        <v>6410487</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119779098</v>
+        <v>119779242</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>567625</v>
       </c>
       <c r="R18" t="n">
-        <v>6410464</v>
+        <v>6410461</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119779223</v>
+        <v>119779265</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567616</v>
+        <v>567592</v>
       </c>
       <c r="R19" t="n">
-        <v>6410471</v>
+        <v>6410490</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119779131</v>
+        <v>119778822</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567618</v>
+        <v>567611</v>
       </c>
       <c r="R20" t="n">
-        <v>6410460</v>
+        <v>6410497</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119779265</v>
+        <v>119779098</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567592</v>
+        <v>567625</v>
       </c>
       <c r="R21" t="n">
-        <v>6410490</v>
+        <v>6410464</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,10 +2904,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119778955</v>
+        <v>119779153</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2916,38 +2916,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2955,10 +2952,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567588</v>
+        <v>567606</v>
       </c>
       <c r="R22" t="n">
-        <v>6410471</v>
+        <v>6410463</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119779279</v>
+        <v>119778854</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3066,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567585</v>
+        <v>567604</v>
       </c>
       <c r="R23" t="n">
-        <v>6410476</v>
+        <v>6410461</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119778822</v>
+        <v>119779131</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3177,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567611</v>
+        <v>567618</v>
       </c>
       <c r="R24" t="n">
-        <v>6410497</v>
+        <v>6410460</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3240,10 +3237,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119779192</v>
+        <v>119779279</v>
       </c>
       <c r="B25" t="n">
-        <v>90582</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,38 +3249,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3291,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567594</v>
+        <v>567585</v>
       </c>
       <c r="R25" t="n">
-        <v>6410459</v>
+        <v>6410476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119779242</v>
+        <v>119779062</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3402,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567625</v>
+        <v>567621</v>
       </c>
       <c r="R26" t="n">
-        <v>6410461</v>
+        <v>6410474</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,10 +3459,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119779255</v>
+        <v>119779211</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3513,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567594</v>
+        <v>567628</v>
       </c>
       <c r="R27" t="n">
-        <v>6410487</v>
+        <v>6410473</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119779062</v>
+        <v>119778981</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3624,10 +3618,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567621</v>
+        <v>567600</v>
       </c>
       <c r="R28" t="n">
-        <v>6410474</v>
+        <v>6410463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3687,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119778981</v>
+        <v>119779192</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>90600</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3699,35 +3693,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3735,10 +3732,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567600</v>
+        <v>567594</v>
       </c>
       <c r="R29" t="n">
-        <v>6410463</v>
+        <v>6410459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3798,10 +3795,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119779153</v>
+        <v>119779223</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3846,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567606</v>
+        <v>567616</v>
       </c>
       <c r="R30" t="n">
-        <v>6410463</v>
+        <v>6410471</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3909,10 +3906,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119779247</v>
+        <v>119779026</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,10 +3954,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567624</v>
+        <v>567602</v>
       </c>
       <c r="R31" t="n">
-        <v>6410463</v>
+        <v>6410466</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4020,10 +4017,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119779211</v>
+        <v>119778955</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4032,35 +4029,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567628</v>
+        <v>567588</v>
       </c>
       <c r="R32" t="n">
-        <v>6410473</v>
+        <v>6410471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 36021-2024 artfynd.xlsx
+++ b/artfynd/A 36021-2024 artfynd.xlsx
@@ -2124,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119778919</v>
+        <v>119778854</v>
       </c>
       <c r="B15" t="n">
-        <v>90984</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,38 +2136,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2175,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567595</v>
+        <v>567604</v>
       </c>
       <c r="R15" t="n">
-        <v>6410463</v>
+        <v>6410461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119779247</v>
+        <v>119779026</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2286,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567624</v>
+        <v>567602</v>
       </c>
       <c r="R16" t="n">
-        <v>6410463</v>
+        <v>6410466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119779255</v>
+        <v>119779242</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2397,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567594</v>
+        <v>567625</v>
       </c>
       <c r="R17" t="n">
-        <v>6410487</v>
+        <v>6410461</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119779242</v>
+        <v>119779255</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2508,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567625</v>
+        <v>567594</v>
       </c>
       <c r="R18" t="n">
-        <v>6410461</v>
+        <v>6410487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119779265</v>
+        <v>119779247</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2619,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567592</v>
+        <v>567624</v>
       </c>
       <c r="R19" t="n">
-        <v>6410490</v>
+        <v>6410463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,7 +2679,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119778822</v>
+        <v>119779265</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2730,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567611</v>
+        <v>567592</v>
       </c>
       <c r="R20" t="n">
-        <v>6410497</v>
+        <v>6410490</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119779098</v>
+        <v>119779153</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2841,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567625</v>
+        <v>567606</v>
       </c>
       <c r="R21" t="n">
-        <v>6410464</v>
+        <v>6410463</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2904,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119779153</v>
+        <v>119778955</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2916,35 +2913,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567606</v>
+        <v>567588</v>
       </c>
       <c r="R22" t="n">
-        <v>6410463</v>
+        <v>6410471</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119778854</v>
+        <v>119779223</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567604</v>
+        <v>567616</v>
       </c>
       <c r="R23" t="n">
-        <v>6410461</v>
+        <v>6410471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119779211</v>
+        <v>119779098</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567628</v>
+        <v>567625</v>
       </c>
       <c r="R27" t="n">
-        <v>6410473</v>
+        <v>6410464</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119778981</v>
+        <v>119778919</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>90984</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3582,35 +3582,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3618,7 +3621,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567600</v>
+        <v>567595</v>
       </c>
       <c r="R28" t="n">
         <v>6410463</v>
@@ -3795,7 +3798,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119779223</v>
+        <v>119778822</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3843,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567616</v>
+        <v>567611</v>
       </c>
       <c r="R30" t="n">
-        <v>6410471</v>
+        <v>6410497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3906,7 +3909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119779026</v>
+        <v>119779211</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3954,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567602</v>
+        <v>567628</v>
       </c>
       <c r="R31" t="n">
-        <v>6410466</v>
+        <v>6410473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4017,10 +4020,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119778955</v>
+        <v>119778981</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4029,38 +4032,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567588</v>
+        <v>567600</v>
       </c>
       <c r="R32" t="n">
-        <v>6410471</v>
+        <v>6410463</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
